--- a/cet4/result/44_宇航女神_星空追梦的传奇/44_宇航女神_星空追梦的传奇_学习版.xlsx
+++ b/cet4/result/44_宇航女神_星空追梦的传奇/44_宇航女神_星空追梦的传奇_学习版.xlsx
@@ -397,745 +397,731 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D51"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>序号</v>
+        <v>词汇</v>
       </c>
       <c r="B1" t="str">
-        <v>单词</v>
+        <v>音标</v>
       </c>
       <c r="C1" t="str">
-        <v>中文释义</v>
+        <v>词性</v>
       </c>
       <c r="D1" t="str">
-        <v>完整形式</v>
+        <v>中文</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2">
-        <v>1</v>
+      <c r="A2" t="str">
+        <v>November</v>
       </c>
       <c r="B2" t="str">
-        <v>November</v>
+        <v>/noʊˈvembər/</v>
       </c>
       <c r="C2" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D2" t="str">
         <v>十一月</v>
       </c>
-      <c r="D2" t="str">
-        <v>November(十一月)📢</v>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
-        <v>2</v>
+      <c r="A3" t="str">
+        <v>federal</v>
       </c>
       <c r="B3" t="str">
-        <v>federal</v>
+        <v>/ˈfedərəl/</v>
       </c>
       <c r="C3" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D3" t="str">
         <v>联邦</v>
       </c>
-      <c r="D3" t="str">
-        <v>federal(联邦)📢</v>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
-        <v>3</v>
+      <c r="A4" t="str">
+        <v>astronaut</v>
       </c>
       <c r="B4" t="str">
-        <v>astronaut</v>
+        <v>/ˈæstrənɔːt/</v>
       </c>
       <c r="C4" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D4" t="str">
         <v>宇航员</v>
       </c>
-      <c r="D4" t="str">
-        <v>astronaut(宇航员)📢</v>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
-        <v>4</v>
+      <c r="A5" t="str">
+        <v>academy</v>
       </c>
       <c r="B5" t="str">
-        <v>academy</v>
+        <v>/əˈkædəmi/</v>
       </c>
       <c r="C5" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D5" t="str">
         <v>学院</v>
       </c>
-      <c r="D5" t="str">
-        <v>academy(学院)📢</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
-        <v>5</v>
+      <c r="A6" t="str">
+        <v>vary</v>
       </c>
       <c r="B6" t="str">
-        <v>vary</v>
+        <v>/ˈveri,ˈværi/</v>
       </c>
       <c r="C6" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D6" t="str">
         <v>变化</v>
       </c>
-      <c r="D6" t="str">
-        <v>vary(变化)📢</v>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
-        <v>6</v>
+      <c r="A7" t="str">
+        <v>crush</v>
       </c>
       <c r="B7" t="str">
-        <v>crush</v>
+        <v>/krʌʃ/</v>
       </c>
       <c r="C7" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D7" t="str">
         <v>压碎</v>
       </c>
-      <c r="D7" t="str">
-        <v>crush(压碎)📢</v>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
-        <v>7</v>
+      <c r="A8" t="str">
+        <v>pulse</v>
       </c>
       <c r="B8" t="str">
-        <v>pulse</v>
+        <v>/pʌls/</v>
       </c>
       <c r="C8" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D8" t="str">
         <v>脉搏</v>
       </c>
-      <c r="D8" t="str">
-        <v>pulse(脉搏)📢</v>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
-        <v>8</v>
+      <c r="A9" t="str">
+        <v>absolutely</v>
       </c>
       <c r="B9" t="str">
-        <v>absolutely</v>
+        <v>/ˈæbsəluːtli/</v>
       </c>
       <c r="C9" t="str">
+        <v>v./adv.</v>
+      </c>
+      <c r="D9" t="str">
         <v>绝对</v>
       </c>
-      <c r="D9" t="str">
-        <v>absolutely(绝对)📢</v>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
-        <v>9</v>
+      <c r="A10" t="str">
+        <v>quilt</v>
       </c>
       <c r="B10" t="str">
-        <v>quilt</v>
+        <v>/kwɪlt/</v>
       </c>
       <c r="C10" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D10" t="str">
         <v>被子</v>
       </c>
-      <c r="D10" t="str">
-        <v>quilt(被子)📢</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
-        <v>10</v>
+      <c r="A11" t="str">
+        <v>execute</v>
       </c>
       <c r="B11" t="str">
-        <v>execute</v>
+        <v>/ˈeksɪkjuːt/</v>
       </c>
       <c r="C11" t="str">
+        <v>vt.</v>
+      </c>
+      <c r="D11" t="str">
         <v>执行</v>
       </c>
-      <c r="D11" t="str">
-        <v>execute(执行)📢</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12">
-        <v>11</v>
+      <c r="A12" t="str">
+        <v>water</v>
       </c>
       <c r="B12" t="str">
-        <v>water</v>
+        <v>/ˈwɔːtər/</v>
       </c>
       <c r="C12" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D12" t="str">
         <v>水</v>
       </c>
-      <c r="D12" t="str">
-        <v>water(水)📢</v>
-      </c>
     </row>
     <row r="13">
-      <c r="A13">
-        <v>12</v>
+      <c r="A13" t="str">
+        <v>coat</v>
       </c>
       <c r="B13" t="str">
-        <v>coat</v>
+        <v>/koʊt/</v>
       </c>
       <c r="C13" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D13" t="str">
         <v>涂层</v>
       </c>
-      <c r="D13" t="str">
-        <v>coat(涂层)📢</v>
-      </c>
     </row>
     <row r="14">
-      <c r="A14">
-        <v>13</v>
+      <c r="A14" t="str">
+        <v>captive</v>
       </c>
       <c r="B14" t="str">
-        <v>captive</v>
+        <v>/ˈkæptɪv/</v>
       </c>
       <c r="C14" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D14" t="str">
         <v>俘虏</v>
       </c>
-      <c r="D14" t="str">
-        <v>captive(俘虏)📢</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15">
-        <v>14</v>
+      <c r="A15" t="str">
+        <v>pretty</v>
       </c>
       <c r="B15" t="str">
-        <v>pretty</v>
+        <v>/ˈprɪti/</v>
       </c>
       <c r="C15" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D15" t="str">
         <v>漂亮的</v>
       </c>
-      <c r="D15" t="str">
-        <v>pretty(漂亮的)📢</v>
-      </c>
     </row>
     <row r="16">
-      <c r="A16">
-        <v>15</v>
+      <c r="A16" t="str">
+        <v>true</v>
       </c>
       <c r="B16" t="str">
-        <v>true</v>
+        <v>/truː/</v>
       </c>
       <c r="C16" t="str">
+        <v>n./vt./v./adj./adv.</v>
+      </c>
+      <c r="D16" t="str">
         <v>真实的</v>
       </c>
-      <c r="D16" t="str">
-        <v>true(真实的)📢</v>
-      </c>
     </row>
     <row r="17">
-      <c r="A17">
-        <v>16</v>
+      <c r="A17" t="str">
+        <v>deep</v>
       </c>
       <c r="B17" t="str">
-        <v>deep</v>
+        <v>/diːp/</v>
       </c>
       <c r="C17" t="str">
+        <v>n./v./adj./adv.</v>
+      </c>
+      <c r="D17" t="str">
         <v>深的</v>
       </c>
-      <c r="D17" t="str">
-        <v>deep(深的)📢</v>
-      </c>
     </row>
     <row r="18">
-      <c r="A18">
-        <v>17</v>
+      <c r="A18" t="str">
+        <v>portable</v>
       </c>
       <c r="B18" t="str">
-        <v>portable</v>
+        <v>/ˈpɔːrtəbl/</v>
       </c>
       <c r="C18" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D18" t="str">
         <v>便携的</v>
       </c>
-      <c r="D18" t="str">
-        <v>portable(便携的)📢</v>
-      </c>
     </row>
     <row r="19">
-      <c r="A19">
-        <v>18</v>
+      <c r="A19" t="str">
+        <v>cellar</v>
       </c>
       <c r="B19" t="str">
-        <v>cellar</v>
+        <v>/ˈselər/</v>
       </c>
       <c r="C19" t="str">
+        <v>n./vt.</v>
+      </c>
+      <c r="D19" t="str">
         <v>地下室</v>
       </c>
-      <c r="D19" t="str">
-        <v>cellar(地下室)📢</v>
-      </c>
     </row>
     <row r="20">
-      <c r="A20">
-        <v>19</v>
+      <c r="A20" t="str">
+        <v>dangerous</v>
       </c>
       <c r="B20" t="str">
-        <v>dangerous</v>
+        <v>/ˈdeɪndʒərəs/</v>
       </c>
       <c r="C20" t="str">
+        <v>adj.</v>
+      </c>
+      <c r="D20" t="str">
         <v>危险的</v>
       </c>
-      <c r="D20" t="str">
-        <v>dangerous(危险的)📢</v>
-      </c>
     </row>
     <row r="21">
-      <c r="A21">
-        <v>20</v>
+      <c r="A21" t="str">
+        <v>judgement</v>
       </c>
       <c r="B21" t="str">
-        <v>judgement</v>
+        <v>/ˈdʒʌdʒmənt/</v>
       </c>
       <c r="C21" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D21" t="str">
         <v>判断</v>
       </c>
-      <c r="D21" t="str">
-        <v>judgement(判断)📢</v>
-      </c>
     </row>
     <row r="22">
-      <c r="A22">
-        <v>21</v>
+      <c r="A22" t="str">
+        <v>loop</v>
       </c>
       <c r="B22" t="str">
-        <v>loop</v>
+        <v>/luːp/</v>
       </c>
       <c r="C22" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D22" t="str">
         <v>回路</v>
       </c>
-      <c r="D22" t="str">
-        <v>loop(回路)📢</v>
-      </c>
     </row>
     <row r="23">
-      <c r="A23">
-        <v>22</v>
+      <c r="A23" t="str">
+        <v>straw</v>
       </c>
       <c r="B23" t="str">
-        <v>straw</v>
+        <v>/strɔː/</v>
       </c>
       <c r="C23" t="str">
+        <v>n./adj.</v>
+      </c>
+      <c r="D23" t="str">
         <v>吸管</v>
       </c>
-      <c r="D23" t="str">
-        <v>straw(吸管)📢</v>
-      </c>
     </row>
     <row r="24">
-      <c r="A24">
-        <v>23</v>
+      <c r="A24" t="str">
+        <v>thin</v>
       </c>
       <c r="B24" t="str">
-        <v>thin</v>
+        <v>/θɪn/</v>
       </c>
       <c r="C24" t="str">
+        <v>n./vt./vi./v./adj./adv.</v>
+      </c>
+      <c r="D24" t="str">
         <v>稀薄的</v>
       </c>
-      <c r="D24" t="str">
-        <v>thin(稀薄的)📢</v>
-      </c>
     </row>
     <row r="25">
-      <c r="A25">
-        <v>24</v>
+      <c r="A25" t="str">
+        <v>telegram</v>
       </c>
       <c r="B25" t="str">
-        <v>telegram</v>
+        <v>/ˈtelɪɡræm/</v>
       </c>
       <c r="C25" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D25" t="str">
         <v>电报</v>
       </c>
-      <c r="D25" t="str">
-        <v>telegram(电报)📢</v>
-      </c>
     </row>
     <row r="26">
-      <c r="A26">
-        <v>25</v>
+      <c r="A26" t="str">
+        <v>delivery</v>
       </c>
       <c r="B26" t="str">
-        <v>delivery</v>
+        <v>/dɪˈlɪvəri/</v>
       </c>
       <c r="C26" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D26" t="str">
         <v>递送</v>
       </c>
-      <c r="D26" t="str">
-        <v>delivery(递送)📢</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27">
-        <v>26</v>
+      <c r="A27" t="str">
+        <v>film</v>
       </c>
       <c r="B27" t="str">
-        <v>film</v>
+        <v>/fɪlm/</v>
       </c>
       <c r="C27" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D27" t="str">
         <v>胶片</v>
       </c>
-      <c r="D27" t="str">
-        <v>film(胶片)📢</v>
-      </c>
     </row>
     <row r="28">
-      <c r="A28">
-        <v>27</v>
+      <c r="A28" t="str">
+        <v>broken</v>
       </c>
       <c r="B28" t="str">
-        <v>broken</v>
+        <v>/ˈbroʊkən/</v>
       </c>
       <c r="C28" t="str">
+        <v>v./adj.</v>
+      </c>
+      <c r="D28" t="str">
         <v>破损的</v>
       </c>
-      <c r="D28" t="str">
-        <v>broken(破损的)📢</v>
-      </c>
     </row>
     <row r="29">
-      <c r="A29">
-        <v>28</v>
+      <c r="A29" t="str">
+        <v>truck</v>
       </c>
       <c r="B29" t="str">
-        <v>truck</v>
+        <v>/trʌk/</v>
       </c>
       <c r="C29" t="str">
+        <v>n./vt./vi./adj.</v>
+      </c>
+      <c r="D29" t="str">
         <v>卡车</v>
       </c>
-      <c r="D29" t="str">
-        <v>truck(卡车)📢</v>
-      </c>
     </row>
     <row r="30">
-      <c r="A30">
-        <v>29</v>
+      <c r="A30" t="str">
+        <v>cannon</v>
       </c>
       <c r="B30" t="str">
-        <v>cannon</v>
+        <v>/ˈkænən/</v>
       </c>
       <c r="C30" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D30" t="str">
         <v>大炮</v>
       </c>
-      <c r="D30" t="str">
-        <v>cannon(大炮)📢</v>
-      </c>
     </row>
     <row r="31">
-      <c r="A31">
-        <v>30</v>
+      <c r="A31" t="str">
+        <v>relief</v>
       </c>
       <c r="B31" t="str">
-        <v>relief</v>
+        <v>/rɪˈliːf/</v>
       </c>
       <c r="C31" t="str">
+        <v>n.</v>
+      </c>
+      <c r="D31" t="str">
         <v>轻松</v>
       </c>
-      <c r="D31" t="str">
-        <v>relief(轻松)📢</v>
-      </c>
     </row>
     <row r="32">
-      <c r="A32">
-        <v>31</v>
+      <c r="A32" t="str">
+        <v>shape</v>
       </c>
       <c r="B32" t="str">
-        <v>shape</v>
+        <v>/ʃeɪp/</v>
       </c>
       <c r="C32" t="str">
+        <v>n./vt./vi.</v>
+      </c>
+      <c r="D32" t="str">
         <v>形状</v>
       </c>
-      <c r="D32" t="str">
-        <v>shape(形状)📢</v>
-      </c>
     </row>
     <row r="33">
-      <c r="A33">
-        <v>32</v>
+      <c r="A33" t="str">
+        <v>natural</v>
       </c>
       <c r="B33" t="str">
-        <v>film</v>
+        <v>/ˈnætʃrəl/</v>
       </c>
       <c r="C33" t="str">
-        <v>拍摄</v>
+        <v>n./adj.</v>
       </c>
       <c r="D33" t="str">
-        <v>film(拍摄)📢</v>
+        <v>自然的</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34">
-        <v>33</v>
+      <c r="A34" t="str">
+        <v>wreck</v>
       </c>
       <c r="B34" t="str">
-        <v>natural</v>
+        <v>/rek/</v>
       </c>
       <c r="C34" t="str">
-        <v>自然的</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D34" t="str">
-        <v>natural(自然的)📢</v>
+        <v>残骸</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35">
-        <v>34</v>
+      <c r="A35" t="str">
+        <v>silence</v>
       </c>
       <c r="B35" t="str">
-        <v>wreck</v>
+        <v>/ˈsaɪləns/</v>
       </c>
       <c r="C35" t="str">
-        <v>残骸</v>
+        <v>n./vt./int.</v>
       </c>
       <c r="D35" t="str">
-        <v>wreck(残骸)📢</v>
+        <v>寂静</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36">
-        <v>35</v>
+      <c r="A36" t="str">
+        <v>wrap</v>
       </c>
       <c r="B36" t="str">
-        <v>silence</v>
+        <v>/ræp/</v>
       </c>
       <c r="C36" t="str">
-        <v>寂静</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D36" t="str">
-        <v>silence(寂静)📢</v>
+        <v>包裹</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37">
-        <v>36</v>
+      <c r="A37" t="str">
+        <v>spoon</v>
       </c>
       <c r="B37" t="str">
-        <v>wrap</v>
+        <v>/spuːn/</v>
       </c>
       <c r="C37" t="str">
-        <v>包裹</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D37" t="str">
-        <v>wrap(包裹)📢</v>
+        <v>勺子</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38">
-        <v>37</v>
+      <c r="A38" t="str">
+        <v>silent</v>
       </c>
       <c r="B38" t="str">
-        <v>spoon</v>
+        <v>/ˈsaɪlənt/</v>
       </c>
       <c r="C38" t="str">
-        <v>勺子</v>
+        <v>n./adj.</v>
       </c>
       <c r="D38" t="str">
-        <v>spoon(勺子)📢</v>
+        <v>寂静的</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39">
-        <v>38</v>
+      <c r="A39" t="str">
+        <v>adjust</v>
       </c>
       <c r="B39" t="str">
-        <v>silent</v>
+        <v>/əˈdʒʌst/</v>
       </c>
       <c r="C39" t="str">
-        <v>寂静的</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D39" t="str">
-        <v>silent(寂静的)📢</v>
+        <v>调整</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40">
-        <v>39</v>
+      <c r="A40" t="str">
+        <v>announce</v>
       </c>
       <c r="B40" t="str">
-        <v>adjust</v>
+        <v>/əˈnaʊns/</v>
       </c>
       <c r="C40" t="str">
-        <v>调整</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D40" t="str">
-        <v>adjust(调整)📢</v>
+        <v>宣布</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41">
-        <v>40</v>
+      <c r="A41" t="str">
+        <v>growth</v>
       </c>
       <c r="B41" t="str">
-        <v>announce</v>
+        <v>/ɡroʊθ/</v>
       </c>
       <c r="C41" t="str">
-        <v>宣布</v>
+        <v>n.</v>
       </c>
       <c r="D41" t="str">
-        <v>announce(宣布)📢</v>
+        <v>成长</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42">
-        <v>41</v>
+      <c r="A42" t="str">
+        <v>contribute</v>
       </c>
       <c r="B42" t="str">
-        <v>growth</v>
+        <v>/kənˈtrɪbjuːt/</v>
       </c>
       <c r="C42" t="str">
-        <v>成长</v>
+        <v>vt./vi.</v>
       </c>
       <c r="D42" t="str">
-        <v>growth(成长)📢</v>
+        <v>贡献</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43">
-        <v>42</v>
+      <c r="A43" t="str">
+        <v>rich</v>
       </c>
       <c r="B43" t="str">
-        <v>contribute</v>
+        <v>/rɪtʃ/</v>
       </c>
       <c r="C43" t="str">
-        <v>贡献</v>
+        <v>n./adj.</v>
       </c>
       <c r="D43" t="str">
-        <v>contribute(贡献)📢</v>
+        <v>丰富的</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44">
-        <v>43</v>
+      <c r="A44" t="str">
+        <v>false</v>
       </c>
       <c r="B44" t="str">
-        <v>rich</v>
+        <v>/fɔːls/</v>
       </c>
       <c r="C44" t="str">
-        <v>丰富的</v>
+        <v>v./adj./adv.</v>
       </c>
       <c r="D44" t="str">
-        <v>rich(丰富的)📢</v>
+        <v>假的</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45">
-        <v>44</v>
+      <c r="A45" t="str">
+        <v>flourish</v>
       </c>
       <c r="B45" t="str">
-        <v>false</v>
+        <v>/ˈflɜːrɪʃ/</v>
       </c>
       <c r="C45" t="str">
-        <v>假的</v>
+        <v>n./v.</v>
       </c>
       <c r="D45" t="str">
-        <v>false(假的)📢</v>
+        <v>繁荣</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46">
-        <v>45</v>
+      <c r="A46" t="str">
+        <v>my</v>
       </c>
       <c r="B46" t="str">
-        <v>flourish</v>
+        <v>/maɪ/</v>
       </c>
       <c r="C46" t="str">
-        <v>繁荣</v>
+        <v>n./pron./int.</v>
       </c>
       <c r="D46" t="str">
-        <v>flourish(繁荣)📢</v>
+        <v>我的</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47">
-        <v>46</v>
+      <c r="A47" t="str">
+        <v>whether</v>
       </c>
       <c r="B47" t="str">
-        <v>my</v>
+        <v>/ˈweðər/</v>
       </c>
       <c r="C47" t="str">
-        <v>我的</v>
+        <v>n./pron./conj.</v>
       </c>
       <c r="D47" t="str">
-        <v>my(我的)📢</v>
+        <v>是否</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48">
-        <v>47</v>
+      <c r="A48" t="str">
+        <v>vote</v>
       </c>
       <c r="B48" t="str">
-        <v>whether</v>
+        <v>/voʊt/</v>
       </c>
       <c r="C48" t="str">
-        <v>是否</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D48" t="str">
-        <v>whether(是否)📢</v>
+        <v>选票</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49">
-        <v>48</v>
+      <c r="A49" t="str">
+        <v>exhaust</v>
       </c>
       <c r="B49" t="str">
-        <v>vote</v>
+        <v>/ɪɡˈzɔːst/</v>
       </c>
       <c r="C49" t="str">
-        <v>选票</v>
+        <v>n./v.</v>
       </c>
       <c r="D49" t="str">
-        <v>vote(选票)📢</v>
+        <v>耗尽</v>
       </c>
     </row>
     <row r="50">
-      <c r="A50">
-        <v>49</v>
+      <c r="A50" t="str">
+        <v>mount</v>
       </c>
       <c r="B50" t="str">
-        <v>exhaust</v>
+        <v>/maʊnt/</v>
       </c>
       <c r="C50" t="str">
-        <v>耗尽</v>
+        <v>n./vt./vi.</v>
       </c>
       <c r="D50" t="str">
-        <v>exhaust(耗尽)📢</v>
+        <v>登上</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51">
-        <v>50</v>
+      <c r="A51" t="str">
+        <v>control</v>
       </c>
       <c r="B51" t="str">
-        <v>mount</v>
+        <v>/kənˈtroʊl/</v>
       </c>
       <c r="C51" t="str">
-        <v>登上</v>
+        <v>n./vt.</v>
       </c>
       <c r="D51" t="str">
-        <v>mount(登上)📢</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="str">
-        <v>control</v>
-      </c>
-      <c r="C52" t="str">
         <v>控制</v>
-      </c>
-      <c r="D52" t="str">
-        <v>control(控制)📢</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D52"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D51"/>
   </ignoredErrors>
 </worksheet>
 </file>